--- a/AAII_Financials/Quarterly/CBRE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBRE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
   <si>
     <t>CBRE</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11226000</v>
+      </c>
+      <c r="E8" s="3">
         <v>10527000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11629000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10258000</v>
       </c>
-      <c r="G8" s="3">
-        <v>9754000</v>
-      </c>
       <c r="H8" s="3">
+        <v>9717000</v>
+      </c>
+      <c r="I8" s="3">
         <v>8875000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10404000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9036000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8391000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7935000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8950000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7868000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7720000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7411000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8194500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7529500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7771300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7332900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8550200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6798300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6458600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5938900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6910500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5645100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5381400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5889200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7119400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5925100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5714100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5135500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6293700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5261000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5111400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4674000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5499700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4638600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>4439600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>4051000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>3823800</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>3193500</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9140000</v>
+      </c>
+      <c r="E9" s="3">
         <v>8675000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9473000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8304000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7942000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7265000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8290000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7252000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6793000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6475000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7067000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6397000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6179000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6006000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6498800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5934500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6054000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5752200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6584300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5258900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5016800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4719500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5370800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4564600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4392100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4712700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5520800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4675900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4436300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4013000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4771600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4098900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3958700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3620000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4150800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3598300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3409500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3146500</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2603100</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>2252800</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2086000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1852000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2156000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1954000</v>
       </c>
-      <c r="G10" s="3">
-        <v>1812000</v>
-      </c>
       <c r="H10" s="3">
+        <v>1775000</v>
+      </c>
+      <c r="I10" s="3">
         <v>1610000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2114000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1784000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1598000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1460000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1883000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1471000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1541000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1405000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1695700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1595000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1717300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1580700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1965900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1539400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1441800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1219400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1539700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1080500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>989300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1176500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1598600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1249200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1277800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1122500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1522100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1162100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1152700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1054000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1348900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1040300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1030100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>904500</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1220700</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>940700</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,65 +1496,68 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-232000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-608000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>24000</v>
       </c>
-      <c r="G14" s="3">
-        <v>58000</v>
-      </c>
       <c r="H14" s="3">
+        <v>59000</v>
+      </c>
+      <c r="I14" s="3">
         <v>68000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-160000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>23000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-13000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-12000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-9000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>136000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>22000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>26400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>10400</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
@@ -1548,32 +1568,32 @@
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>89100</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>37600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>75200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>800</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>91600</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
@@ -1581,14 +1601,14 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>28000</v>
       </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AL14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
       <c r="AM14" s="3">
         <v>0</v>
       </c>
@@ -1601,130 +1621,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>190000</v>
+      </c>
+      <c r="E15" s="3">
         <v>182000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>189000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>181000</v>
       </c>
-      <c r="G15" s="3">
-        <v>182000</v>
-      </c>
       <c r="H15" s="3">
+        <v>145000</v>
+      </c>
+      <c r="I15" s="3">
         <v>142000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>177000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>178000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>161000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>158000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>148000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>149000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>155000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>162000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>159600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>142100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>162400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>149000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>162100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>122600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>119100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>122100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>143800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>127700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>116400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>113800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>122700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>118200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>112200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>111700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>116900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>113500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>113400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>108200</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>109100</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>102600</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>100400</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>94000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>96900</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>92700</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10821000</v>
+      </c>
+      <c r="E17" s="3">
         <v>10248000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11615000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9753000</v>
       </c>
-      <c r="G17" s="3">
-        <v>9324000</v>
-      </c>
       <c r="H17" s="3">
+        <v>9286000</v>
+      </c>
+      <c r="I17" s="3">
         <v>8531000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9970000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8645000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8132000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7744000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8424000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7599000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7423000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7238000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7950800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7157100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7254300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6956000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7958000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6388700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6092100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5669800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6542200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5433700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5287200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5668900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6605600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5608500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5429700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4993100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5834400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5071200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4886100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4488300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5093500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4399600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4211200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3845800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3471000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3021000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>405000</v>
+      </c>
+      <c r="E18" s="3">
         <v>279000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>14000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>505000</v>
       </c>
-      <c r="G18" s="3">
-        <v>430000</v>
-      </c>
       <c r="H18" s="3">
+        <v>431000</v>
+      </c>
+      <c r="I18" s="3">
         <v>344000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>434000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>391000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>259000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>191000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>526000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>269000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>297000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>173000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>243700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>372400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>517000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>376900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>592200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>409600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>366500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>269100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>368300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>211400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>94200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>220300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>513800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>316600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>284400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>142400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>459300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>189800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>225300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>185700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>406200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>239000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>228400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>205200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>352800</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>172500</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,297 +2085,304 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-56000</v>
       </c>
-      <c r="G20" s="3">
-        <v>13000</v>
-      </c>
       <c r="H20" s="3">
+        <v>12000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-17000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-71000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-8000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>9000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>49000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-132000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-144000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-183100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>221900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>93700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>15600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>324900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>160500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>210400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>76200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>42100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>22500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>6700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>4400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>25300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>4900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>95100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>61700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>223500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>101600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>39500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>55100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>72700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>80000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>21500</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>79200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>605000</v>
+      </c>
+      <c r="E21" s="3">
         <v>463000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>202000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>742000</v>
       </c>
-      <c r="G21" s="3">
-        <v>599000</v>
-      </c>
       <c r="H21" s="3">
+        <v>564000</v>
+      </c>
+      <c r="I21" s="3">
         <v>503000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>682000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>577000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>411000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>300000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>806000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>419000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>450000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>479000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>220200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>736500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>773000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>541600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1079200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>692700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>696000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>467400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>554300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>361600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>217300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>338500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>654500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>433100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>392400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>343300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>637900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>526800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>440200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>333300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>570500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>414300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>408700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>320800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>529000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>292300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E22" s="3">
         <v>59000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>57000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>50000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>59000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>50000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>52000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>64000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>63000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>36000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>39000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>38000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>43000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>28000</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2367,8 +2407,8 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>8</v>
@@ -2385,285 +2425,294 @@
       <c r="AE22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AF22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG22" s="3">
         <v>22700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>24900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>26700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>26900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>28900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>32900</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>34500</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>35400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>34000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>35800</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>37300</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>315000</v>
+      </c>
+      <c r="E23" s="3">
         <v>454000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>564000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>487000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>301000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>243000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>613000</v>
+      </c>
+      <c r="K23" s="3">
+        <v>312000</v>
+      </c>
+      <c r="L23" s="3">
+        <v>174000</v>
+      </c>
+      <c r="M23" s="3">
+        <v>119000</v>
+      </c>
+      <c r="N23" s="3">
+        <v>631000</v>
+      </c>
+      <c r="O23" s="3">
+        <v>232000</v>
+      </c>
+      <c r="P23" s="3">
+        <v>261000</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>153000</v>
+      </c>
+      <c r="R23" s="3">
+        <v>60600</v>
+      </c>
+      <c r="S23" s="3">
+        <v>594300</v>
+      </c>
+      <c r="T23" s="3">
+        <v>610700</v>
+      </c>
+      <c r="U23" s="3">
+        <v>392500</v>
+      </c>
+      <c r="V23" s="3">
+        <v>917100</v>
+      </c>
+      <c r="W23" s="3">
+        <v>570100</v>
+      </c>
+      <c r="X23" s="3">
+        <v>576900</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>345300</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>410400</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>233900</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>100900</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>224700</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>539200</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>321500</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>286000</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>214700</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>496100</v>
+      </c>
+      <c r="AI23" s="3">
+        <v>386700</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>300000</v>
       </c>
-      <c r="H23" s="3">
-        <v>243000</v>
-      </c>
-      <c r="I23" s="3">
-        <v>613000</v>
-      </c>
-      <c r="J23" s="3">
-        <v>312000</v>
-      </c>
-      <c r="K23" s="3">
-        <v>174000</v>
-      </c>
-      <c r="L23" s="3">
-        <v>119000</v>
-      </c>
-      <c r="M23" s="3">
-        <v>631000</v>
-      </c>
-      <c r="N23" s="3">
-        <v>232000</v>
-      </c>
-      <c r="O23" s="3">
-        <v>261000</v>
-      </c>
-      <c r="P23" s="3">
-        <v>153000</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>60600</v>
-      </c>
-      <c r="R23" s="3">
-        <v>594300</v>
-      </c>
-      <c r="S23" s="3">
-        <v>610700</v>
-      </c>
-      <c r="T23" s="3">
-        <v>392500</v>
-      </c>
-      <c r="U23" s="3">
-        <v>917100</v>
-      </c>
-      <c r="V23" s="3">
-        <v>570100</v>
-      </c>
-      <c r="W23" s="3">
-        <v>576900</v>
-      </c>
-      <c r="X23" s="3">
-        <v>345300</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>410400</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>233900</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>100900</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>224700</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>539200</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>321500</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>286000</v>
-      </c>
-      <c r="AF23" s="3">
-        <v>214700</v>
-      </c>
-      <c r="AG23" s="3">
-        <v>496100</v>
-      </c>
-      <c r="AH23" s="3">
-        <v>386700</v>
-      </c>
-      <c r="AI23" s="3">
-        <v>300000</v>
-      </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>196300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>428500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>277200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>272900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>192700</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>396200</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>162300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E24" s="3">
         <v>112000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>114000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>91000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>61000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>52000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>112000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>67000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>32000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-29000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>136000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>31000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>55000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>28000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-25500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>142700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>120800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-3700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>224200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>133500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>133400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>76300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>95100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>49100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>18800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>51200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-100000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>63500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>62500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>43900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>88900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>95000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>70300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>45600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>123600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>77100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>69900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>53800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>131100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>51400</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>247000</v>
+      </c>
+      <c r="E26" s="3">
         <v>342000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>450000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>396000</v>
       </c>
-      <c r="G26" s="3">
-        <v>239000</v>
-      </c>
       <c r="H26" s="3">
+        <v>240000</v>
+      </c>
+      <c r="I26" s="3">
         <v>191000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>501000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>245000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>142000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>148000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>495000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>201000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>206000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>125000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>86100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>451700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>489900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>396300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>692900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>436600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>443400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>269000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>315400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>184800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>82100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>173500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>639100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>258100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>223400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>170800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>407300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>291700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>229600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>150700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>304900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>200100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>203000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>138900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>265100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>110900</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E27" s="3">
         <v>318000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>416000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>363000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>215000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>163000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>487000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>225000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>130000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>126000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>477000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>191000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>201000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>117000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>81100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>446600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>487300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>392300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>692000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>435700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>442600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>266200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>313800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>184100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>81900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>172200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>637600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>256600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>223700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>164400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>406500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>290500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>228700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>150800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>302600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>199100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>201800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>137000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>264000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3224,17 +3285,17 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
+      <c r="AC29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -3242,23 +3303,23 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-12800</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
         <v>0</v>
       </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-500</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-143400</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E32" s="3">
         <v>2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>56000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-13000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I32" s="3">
         <v>17000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>71000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>8000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-9000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-49000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>132000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>144000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>183100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-221900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-93700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-15600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-324900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-160500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-210400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-76200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-42100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-22500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-25300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-4900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-95100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-61700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-223500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-101600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-39500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-55100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-72700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-80000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-21500</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-79200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-27000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E33" s="3">
         <v>318000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>416000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>363000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>215000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>163000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>487000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>225000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>130000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>126000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>477000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>191000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>201000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>117000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>81100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>446600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>487300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>392300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>692000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>435700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>442600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>266200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>313800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>184100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>81900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>172200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>637600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>256600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>223700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>164400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>393800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>290500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>228700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>150300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>159200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>199100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>201800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>137000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>264000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E35" s="3">
         <v>318000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>416000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>363000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>215000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>163000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>487000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>225000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>130000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>126000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>477000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>191000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>201000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>117000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>81100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>446600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>487300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>392300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>692000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>435700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>442600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>266200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>313800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>184100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>81900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>172200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>637600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>256600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>223700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>164400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>393800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>290500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>228700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>150300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>159200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>199100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>201800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>137000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>264000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1489000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1664000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1864000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1669000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1395000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1382000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1114000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1025000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>928000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1044000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1265000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1252100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1261200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1231300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1318300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1125000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1192800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1657300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2431000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2767800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2142800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1910300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1896200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1481900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1214200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>628500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>971800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>577500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>535600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>605000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>777200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>550500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>531500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>642900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>751800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>955600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>535700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>533300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>762600</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>446300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,130 +4553,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9495000</v>
+      </c>
+      <c r="E43" s="3">
         <v>9071000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8921000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8177000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8007000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7267000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7535000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7358000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6948000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6796000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6972000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6295300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6114900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5993900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6255300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6520200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6522300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6663800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6837000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6369100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5981200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5304200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6218100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5554700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5291900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5953700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5881700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5432900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5743900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5703500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5389800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5223400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4969900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4544800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4363000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>4344400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3778800</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3239700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3927300</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>4130100</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,618 +4803,636 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>648000</v>
+      </c>
+      <c r="E45" s="3">
         <v>539000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>552000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>525000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>553000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>527000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>321000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>302000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>357000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>365000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>315000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>343100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>635000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>611100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>955100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>944800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1157100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1012400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>814400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>938500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>762900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>691800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>731400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>734800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>683300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>681500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>681000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1048500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>605700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>688400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>587200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>604500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>605400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>566700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>515800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>504700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>509800</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>472500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>432600</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>479000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12912000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12734000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13489000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12573000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11960000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10831000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9970000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10616000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9653000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9444000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9666000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9326600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9469700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9046400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8528700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8590000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8872200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9333500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10082400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10075400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8886900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7906300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8845600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>7771400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>7189400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>7263600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7534500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7058800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6885200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6996900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6754200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6378300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6106700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5754300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>5630600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5804700</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>4824300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4245500</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>5122500</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>5055500</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>983000</v>
+      </c>
+      <c r="E47" s="3">
         <v>973000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1000000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1017000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1006000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1130000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1443000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1477000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1451800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1440800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1517000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1316400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1306800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1295100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1507100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1638600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1391200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1296600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1369300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1017600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>904900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>855300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>649600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>609800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>610100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>653100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>775700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>328600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>307300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>228400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>216200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>195300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>233900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>229000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>238000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>233600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>246700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>242500</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>232200</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>249900</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3485000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3423000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3445000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3282000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3249000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3107000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2372000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2289000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2137000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2113000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2147000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1947600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1931600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1904500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1960100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1847500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1912300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1931100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1973300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1809700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1860700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1889500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1953200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1976300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1986300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1897100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1928300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1842600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1763900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1728800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>721700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>702400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>705500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>633700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>617700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>574300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>556500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>551600</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>560800</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>550800</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9842000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9939000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10023000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8830000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8895000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8757000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7919000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8150000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8052000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7852000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7210000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7025800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7173600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7086800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7061100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6807100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7051500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7315600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7404600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5220400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5237300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5175200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5189500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5078200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5026300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5013500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5133000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4952900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4995100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5002500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5093600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5046600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4855500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4677100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4653900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>4535900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>4494700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>4422800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>4392400</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>4459900</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2461000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2276000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2120000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2052000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1824000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1893000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2052000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1825000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1738200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1673200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1563000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1643100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1403600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1283800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1456400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1332100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1211500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1266300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1243900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1607300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1568600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1422500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1401300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>911400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>888200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>852900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>825700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>858000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>767600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>736400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>671100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>654500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>633900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>613400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>578200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>503500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>484000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>464700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>471700</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>460700</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30471000</v>
+      </c>
+      <c r="E54" s="3">
         <v>30170000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>30877000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>28566000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27693000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>26366000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>24383000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>24845000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23462000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>22964000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>22548000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21687400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21732100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21030100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>20513400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>20215300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>20438700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>21143200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>22073500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>19730400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>18458400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17248700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>18039100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>16347100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>15700400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>15680300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>16197200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>15040900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>14719100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>14693000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>13456800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12977100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12535500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>11907400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>11718400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>11652000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>10606200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>9927100</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>10779600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>10776800</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4802000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4574000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4689000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4204000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3891000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3735000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3903000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3543000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3300400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3150000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3298000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2868700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2886200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2945800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3078800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2720500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2825500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2881900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2916300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2604600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2485100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2469400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2692900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2428800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2329200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2365000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2436100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2085400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2063800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1833800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1919800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1674200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1642000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1505100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1573700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1505900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1427400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1320600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1446400</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1365500</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2759000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3295000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2889000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3115000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3198000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3763000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1185000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2417000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2216000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1969000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>969000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1943600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2301100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2708600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1129600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1527800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1396800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1450000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1348200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1425000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1145100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>718200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1430100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1236200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1248200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1302700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1018500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1437100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1609400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1924800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1331900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1724700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2071100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1611100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>910800</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1416300</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1055000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>791500</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1254700</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1747100</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1233000</v>
+        <v>974000</v>
       </c>
       <c r="E59" s="3">
         <v>1233000</v>
       </c>
       <c r="F59" s="3">
+        <v>1233000</v>
+      </c>
+      <c r="G59" s="3">
         <v>1055000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1100000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1071000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1085000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1006000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>908600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>943000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>961000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>588200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>586300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>719900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4033600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3507400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3401500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3457900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4154300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3405900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2767800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2585200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3020900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2487300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2275500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2397700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2981900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2505500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2214200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2251500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2551600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2086900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1668000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1753400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2228500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1629200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1315200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1361100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1824300</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1454200</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11317000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11753000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12320000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11152000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10623000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10868000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9287000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9430000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8629000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8233000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8243000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7866600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8153000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8717500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8242000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7755700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7623800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7789800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8418900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7435600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6398000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5772800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7144000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6152300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5852900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6065400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6436500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6028000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5887400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6010100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5803400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5485800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5381100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4869700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>4712900</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4551400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>3797600</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>3473200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>4525400</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>4566900</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8047000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7286000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7338000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6561000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6531000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5279000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4674000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4570000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4438000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4411000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3965000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3920400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3174900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2196200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1143800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1533000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1564100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1597000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1611400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1921300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1934700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1926800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1459100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1845500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1825700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1817500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1821200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1798500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1807600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1794500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1767300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1760000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1762900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1758200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1999600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2551600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2550400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2549300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2548100</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2614900</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1687000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1585000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1280000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1318000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1288000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>970000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>913000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1036000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>958000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>968000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>933000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1171400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1230400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1197300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2521900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2287100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2355800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2473500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2684100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1972900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2002500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1893300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1930400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1755000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1736800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1627800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1666400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1655500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1633600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1684200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>876300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>958900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>874600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>860900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>831200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>697200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>675200</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>646400</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>648800</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>613500</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21297000</v>
+      </c>
+      <c r="E66" s="3">
         <v>20863000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>21251000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>19273000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>18700000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17362000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15191000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15289000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14273000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13865000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13481000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13226500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12838400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12387700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12660100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12279500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12302700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12673200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13545300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11767800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10778800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10018400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10960800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9794000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>9456400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9550900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9964500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9529100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9372500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>9603600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>8518000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>8264200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>8081900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7549800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>7603900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>7856500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>7066500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>6715200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>7765100</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>7841700</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9512000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9678000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9916000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9768000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9393000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9386000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9567000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9584000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9384000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9263000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9188000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8724700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9011200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8809800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8832900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9155700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>9084400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8758900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8366600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7674600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7238900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6796300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6530100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6216300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6032200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5950300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5793100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5155500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4898900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4675200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4504700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4110900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>3820400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>3591800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>3443000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>3180000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>2983700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>2786500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>2656900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>2392900</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8398000</v>
+      </c>
+      <c r="E76" s="3">
         <v>8520000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8878000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8535000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8253000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8282000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8411000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8692000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8356000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8261000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8267000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7684000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8098100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7859800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7853300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7935800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8136000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8470000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8528200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7962600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7679500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7230400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7078300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6553100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6244000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6129300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6232700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5511800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5346600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5089400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4938800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4713000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4453600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4357600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4114500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3795500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3539700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3211900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>3014500</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>2935000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E81" s="3">
         <v>318000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>416000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>363000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>215000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>163000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>487000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>225000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>130000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>126000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>477000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>191000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>201000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>117000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>81100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>446600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>487300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>392300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>692000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>435700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>442600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>266200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>313800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>184100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>81900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>172200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>637600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>256600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>223700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>164400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>393800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>290500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>228700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>150300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>159200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>199100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>201800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>137000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>264000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>104200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>163000</v>
+      </c>
+      <c r="E83" s="3">
         <v>155000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>232000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>190000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>172000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>171000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>182000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>113700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>116800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>125500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>177900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>102700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>117700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>108000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>159600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>142100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>162400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>149000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>162100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>122600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>119100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>122100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>143800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>127700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>116400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>113800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>115400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>111600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>106500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>105800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>116900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>113500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>113400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>108200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>109100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>102600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>100400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>94000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>96900</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>92700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>138000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-825000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1221000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>827000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>57000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-546000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1340000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>573000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>287000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-492000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>853000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>383000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-11000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-745000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>814300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>753900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>454400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-393500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1164100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>973000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>420600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-193400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>940400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>866200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>152900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-128800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1048600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>468000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>99300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-392600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>628900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>594400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>157900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-250000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>508800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>503000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>204000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-321400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>503500</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>156800</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-81000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-144000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-84000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-74000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-64000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-93000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-79000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-67000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-68000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-94000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-76000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-75000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-60000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-99100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-64300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-54700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-42100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-88400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-45500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-46300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-29600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-76000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-56400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-71900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-62200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-132900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-59900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-53000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-47700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-75900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-44400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-60800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-46700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-76400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-41700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-36100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-47500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-56800</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-55300</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-273000</v>
+      </c>
+      <c r="E94" s="3">
         <v>64000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-963000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-197000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-462000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-20000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-187000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-407000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-900000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-144000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-167000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-255000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-115000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-228700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-274800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-233300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-95600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-725500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-210900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-150600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-193900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-135100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-70500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-43700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-92200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-484800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-111700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-64600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-106600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-77500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-312400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-64200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-107600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>5100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-18400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-20500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>32200</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,8 +10455,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10266,8 +10500,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E100" s="3">
         <v>545000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-36000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-328000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-96000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1256000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1148000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-315000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>50000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1192000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-752000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-169000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>314000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>761000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-553400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-452200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-551500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-209000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-765500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-104200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-22900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>402000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-111400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-488300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>470900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-93900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-220000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-237900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-114100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>300000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-293100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-479500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>84700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>181300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-559600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-29600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-132400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>117800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-198800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-142300</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E101" s="3">
         <v>44000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-108000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>53000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-24000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-44000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>61000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-51000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-11000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>14000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>149100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-134500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-131500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-49000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>149600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-134500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-131500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-49000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-9400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-38600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>8100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-52200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>71600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>37100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>11500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-38600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>12100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-17400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>14500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-9800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>6800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-12800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-48600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>29800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>8500</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>4000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>16200</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-20700</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-156000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-219000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>205000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>277000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>19000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>292000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>64000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>124000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-94000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-244000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>18000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>37000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-85000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>181800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-107700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-461900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-747200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-336300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>619300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>255100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-37500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>392700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>332800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>581000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-361100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>391400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>89100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-74400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-176300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>236000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>24600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-118500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-103000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-215600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>430000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>8300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-229300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>316200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>14600</v>
       </c>
     </row>
